--- a/шаблони/комплекти/Стрільби/Шаблон_Відомість допуску до стрільб (Додаток 5).xlsx
+++ b/шаблони/комплекти/Стрільби/Шаблон_Відомість допуску до стрільб (Додаток 5).xlsx
@@ -63,7 +63,7 @@
     <x:t>заняття з основ та правил стрільби</x:t>
   </x:si>
   <x:si>
-    <x:t>зайняття з вивчення матеріальної частини озброєння</x:t>
+    <x:t>заняття з вивчення матеріальної частини озброєння</x:t>
   </x:si>
   <x:si>
     <x:t>виконання нормативів</x:t>
@@ -72,38 +72,37 @@
     <x:t>розвідка цілей, визначення дальності та цілевказування</x:t>
   </x:si>
   <x:si>
+    <x:t>{{№}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>слухач</x:t>
   </x:si>
   <x:si>
+    <x:t>{{звання}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{{піб}}</x:t>
   </x:si>
   <x:si>
     <x:t>{{оцінка_1}}</x:t>
   </x:si>
   <x:si>
+    <x:t>{{оцінка_2}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{оцінка_3}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{оцінка_4}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{оцінка_загальна}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>"допущений"</x:t>
   </x:si>
   <x:si>
-    <x:t>{{звання}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{№}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{оцінка_3}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{оцінка_2}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{оцінка_4}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{оцінка_загальна}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Начальник курсів перепідготовки та підвищення кваліфікації 
-Харківського національного університету Повітряних Сил
+    <x:t xml:space="preserve">{{посада_підписанта}}
 {{звання_підписанта}}                                                                            {{піб_підписанта}}                                                                                                 
 {{дата_аркуша}} р.
 </x:t>
@@ -668,34 +667,34 @@
     </x:row>
     <x:row r="7" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="B7" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="15" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="15" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G7" s="15" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I7" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J7" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J7" s="15" t="s">
+      <x:c r="K7" s="15" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="K7" s="15" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.3">
